--- a/test/excel/cond/files/kinds-move.xlsx
+++ b/test/excel/cond/files/kinds-move.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fcond-43137/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fcond-66268/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9AEB74A-F047-BD46-8450-B11F06E983AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78CF5126-C643-F04B-A092-B1E114539DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,26 +1087,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D1:D11">
-    <cfRule type="timePeriod" dxfId="13" priority="7" timePeriod="lastMonth">
+    <cfRule type="timePeriod" dxfId="13" priority="6" timePeriod="lastMonth">
       <formula>AND(MONTH(D1)=MONTH(EDATE(TODAY(),0-1)),YEAR(D1)=YEAR(EDATE(TODAY(),0-1)))</formula>
     </cfRule>
-    <cfRule type="containsBlanks" dxfId="12" priority="8">
+    <cfRule type="containsBlanks" dxfId="12" priority="7">
       <formula>LEN(TRIM(D1))=0</formula>
     </cfRule>
-    <cfRule type="notContainsErrors" dxfId="11" priority="9">
+    <cfRule type="notContainsErrors" dxfId="11" priority="8">
       <formula>NOT(ISERROR(D1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E11">
-    <cfRule type="top10" dxfId="10" priority="10" percent="1" bottom="1" rank="30"/>
-    <cfRule type="aboveAverage" dxfId="9" priority="11" aboveAverage="0" equalAverage="1"/>
+    <cfRule type="top10" dxfId="10" priority="9" percent="1" bottom="1" rank="30"/>
+    <cfRule type="aboveAverage" dxfId="9" priority="10" aboveAverage="0" stdDev="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F11">
-    <cfRule type="uniqueValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="uniqueValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G11">
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="40"/>
@@ -1118,11 +1118,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H11">
-    <cfRule type="dataBar" priority="15">
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{00000001-0000-4000-8000-00000000000E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I1:I11">
+    <cfRule type="dataBar" priority="15">
+      <dataBar showValue="0">
+        <cfvo type="num" val="-5"/>
+        <cfvo type="percentile" val="90"/>
+        <color rgb="FFFFB628"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -1131,22 +1145,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I11">
+  <conditionalFormatting sqref="J1:J11">
     <cfRule type="dataBar" priority="16">
-      <dataBar showValue="0">
-        <cfvo type="num" val="-5"/>
-        <cfvo type="percentile" val="90"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00000001-0000-4000-8000-000000000010}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J11">
-    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1155,7 +1155,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1:K11">
-    <cfRule type="iconSet" priority="18">
+    <cfRule type="iconSet" priority="17">
       <iconSet iconSet="5Quarters" reverse="1">
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="20"/>
@@ -1172,21 +1172,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R5 B6:B11">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="3" priority="22">
       <formula>AND($R1&gt;2,ISODD($R1))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:S5 C6:C11">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",C1)))</formula>
     </cfRule>
-    <cfRule type="beginsWith" priority="4" operator="beginsWith" text="a&quot;b">
+    <cfRule type="beginsWith" priority="3" operator="beginsWith" text="a&quot;b">
       <formula>LEFT(C1,LEN("a""b"))="a""b"</formula>
     </cfRule>
-    <cfRule type="endsWith" dxfId="1" priority="5" operator="endsWith" text="z">
+    <cfRule type="endsWith" dxfId="1" priority="4" operator="endsWith" text="z">
       <formula>RIGHT(C1,LEN("z"))="z"</formula>
     </cfRule>
-    <cfRule type="notContainsText" dxfId="0" priority="6" operator="notContains" text="q">
+    <cfRule type="notContainsText" dxfId="0" priority="5" operator="notContains" text="q">
       <formula>ISERROR(SEARCH("q",C1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1195,7 +1195,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00000001-0000-4000-8000-00000000000F}">
+          <x14:cfRule type="dataBar" id="{00000001-0000-4000-8000-00000000000E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -1208,7 +1208,7 @@
           <xm:sqref>H1:H11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00000001-0000-4000-8000-000000000010}">
+          <x14:cfRule type="dataBar" id="{00000001-0000-4000-8000-00000000000F}">
             <x14:dataBar gradient="0" direction="rightToLeft" negativeBarColorSameAsPositive="1" axisPosition="middle">
               <x14:cfvo type="num">
                 <xm:f>-5</xm:f>
@@ -1222,7 +1222,7 @@
           <xm:sqref>I1:I11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{00000001-0000-4000-8000-000000000013}">
+          <x14:cfRule type="iconSet" priority="18" id="{00000001-0000-4000-8000-000000000012}">
             <x14:iconSet iconSet="3Stars" showValue="0">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -1238,7 +1238,7 @@
           <xm:sqref>L1:L11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{00000001-0000-4000-8000-000000000014}">
+          <x14:cfRule type="iconSet" priority="19" id="{00000001-0000-4000-8000-000000000013}">
             <x14:iconSet custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -1257,7 +1257,7 @@
           <xm:sqref>M1:M11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="21" id="{00000001-0000-4000-8000-000000000015}">
+          <x14:cfRule type="expression" priority="20" id="{00000001-0000-4000-8000-000000000014}">
             <xm:f>$N1&gt;'Other sheet'!$A$1</xm:f>
             <x14:dxf>
               <fill>
@@ -1270,7 +1270,7 @@
           <xm:sqref>N1:N11</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="22" operator="greaterThan" id="{00000001-0000-4000-8000-000000000016}">
+          <x14:cfRule type="cellIs" priority="21" operator="greaterThan" id="{00000001-0000-4000-8000-000000000015}">
             <xm:f>'Other sheet'!$A$2</xm:f>
             <x14:dxf>
               <font>
